--- a/data/trans_bre/P1410-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P1410-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,4</t>
+          <t>-0,54</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-7,06%</t>
+          <t>-9,47%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 2,25</t>
+          <t>-1,87; 2,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 3,48</t>
+          <t>-0,9; 3,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 4,62</t>
+          <t>-0,39; 4,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 1,63</t>
+          <t>-2,38; 1,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-37,65; 76,93</t>
+          <t>-36,3; 74,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-23,08; 144,63</t>
+          <t>-21,97; 138,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 141,88</t>
+          <t>-9,62; 140,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-38,18; 37,0</t>
+          <t>-35,48; 36,4</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>-0,12</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>-2,73%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 1,42</t>
+          <t>-2,29; 1,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 2,22</t>
+          <t>-1,42; 2,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 0,99</t>
+          <t>-2,25; 1,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 2,89</t>
+          <t>-1,67; 1,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-42,41; 43,98</t>
+          <t>-43,55; 40,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-31,4; 74,33</t>
+          <t>-28,3; 73,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-50,11; 34,05</t>
+          <t>-47,76; 36,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-21,6; 143,99</t>
+          <t>-30,95; 39,14</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-3,66</t>
+          <t>-2,53</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-58,35%</t>
+          <t>-42,4%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 1,69</t>
+          <t>-3,18; 1,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 1,18</t>
+          <t>-2,59; 1,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 2,81</t>
+          <t>-1,35; 2,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,96; -1,58</t>
+          <t>-4,89; -0,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-44,26; 44,04</t>
+          <t>-47,8; 36,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-54,82; 49,35</t>
+          <t>-56,4; 55,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-27,25; 96,68</t>
+          <t>-30,54; 92,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-82,69; -33,49</t>
+          <t>-64,35; -14,51</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,56</t>
+          <t>-1,19</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-27,17%</t>
+          <t>-21,0%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,5; -0,31</t>
+          <t>-3,8; -0,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 2,1</t>
+          <t>-1,86; 2,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 2,94</t>
+          <t>-0,58; 3,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 0,17</t>
+          <t>-2,83; 0,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-62,96; -7,21</t>
+          <t>-64,94; -9,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-28,54; 60,79</t>
+          <t>-33,52; 56,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,34; 127,17</t>
+          <t>-15,17; 131,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-49,88; 3,39</t>
+          <t>-42,93; 11,01</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,08</t>
+          <t>-1,04</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-21,13%</t>
+          <t>-19,21%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 0,25</t>
+          <t>-1,77; 0,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1,26</t>
+          <t>-0,7; 1,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,85</t>
+          <t>-0,26; 1,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 0,28</t>
+          <t>-2,02; -0,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-36,45; 6,14</t>
+          <t>-35,35; 3,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,79; 39,18</t>
+          <t>-16,87; 36,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 55,83</t>
+          <t>-6,03; 53,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-36,57; 4,99</t>
+          <t>-33,81; -3,76</t>
         </is>
       </c>
     </row>
